--- a/Table/UnitSpriteTable.xlsx
+++ b/Table/UnitSpriteTable.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="82">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -27,14 +27,6 @@
   </si>
   <si>
     <t>UnitType-int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PartType-int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Path-string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -162,58 +154,6 @@
   </si>
   <si>
     <t>세트 지정이 필요할 경우 사용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>head</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair07</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair08</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair09</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>backhair01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -271,6 +211,146 @@
 2. 뒷머리
 3. 얼굴 장식
 4. 모자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Label-string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Category-string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackHair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Face</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 기본 표정 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 기본 표정 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 기본 표정 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FaceDeco</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 콧수염 12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비 콧수염 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비 콧수염 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비 콧수염 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비 콧수염 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비 콧수염 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비 콧수염 6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비 콧수염 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비 콧수염 8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -295,12 +375,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -317,7 +409,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -326,6 +418,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,14 +732,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="32.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -650,16 +751,16 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -667,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
@@ -675,471 +776,931 @@
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="1">
-        <v>0</v>
+      <c r="E2" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>37</v>
+      <c r="B3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>38</v>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>39</v>
+      <c r="B5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>40</v>
+      <c r="B6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>41</v>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>42</v>
+      <c r="B8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>43</v>
+      <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>44</v>
+      <c r="B10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>45</v>
+      <c r="B11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>46</v>
+      <c r="B12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>47</v>
+      <c r="B13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
-        <v>2</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>48</v>
+      <c r="B14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>37</v>
+      <c r="B15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>38</v>
+      <c r="B16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>39</v>
+      <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>40</v>
+      <c r="B18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>41</v>
+      <c r="B19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>42</v>
+      <c r="B20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="4">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>43</v>
+      <c r="B21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>44</v>
+      <c r="B22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>45</v>
+      <c r="B23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>46</v>
+      <c r="B24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="4">
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>47</v>
+      <c r="B25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="4">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="4">
+        <v>0</v>
+      </c>
+      <c r="D30" s="4">
+        <v>2</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3">
+        <v>2</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3">
+        <v>2</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3">
+        <v>2</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="4">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4">
+        <v>2</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="4">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4">
+        <v>2</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="4">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4">
+        <v>2</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="4">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="4">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4">
+        <v>2</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F43" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="4">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4">
+        <v>2</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="4">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4">
+        <v>2</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="4">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4">
+        <v>2</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F46" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="4">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F47" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="4">
+        <v>0</v>
+      </c>
+      <c r="D48" s="4">
+        <v>2</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F48" s="4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1161,13 +1722,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1175,64 +1736,64 @@
     </row>
     <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="99" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
